--- a/selenium_model/APPIUM_END_TO_END_FINAL_REPORT.xlsx
+++ b/selenium_model/APPIUM_END_TO_END_FINAL_REPORT.xlsx
@@ -2153,7 +2153,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -13950,7 +13950,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -15595,7 +15595,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
